--- a/data_lake/behavior/NAAIM Exposure Index.xlsx
+++ b/data_lake/behavior/NAAIM Exposure Index.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/behavior/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91626206-E925-7741-A753-959BC23783D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2415F98-7765-F74B-B77A-5ED244BC991D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15020" yWindow="780" windowWidth="20980" windowHeight="20700" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15020" yWindow="780" windowWidth="20980" windowHeight="20700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NAAIM" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="42">
   <si>
     <t>average</t>
   </si>
@@ -164,6 +164,9 @@
   <si>
     <t>https://ycharts.com/indicators/naaim_number</t>
     <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>UTC-4</t>
   </si>
 </sst>
 </file>
@@ -4038,6 +4041,9 @@
                 <c:pt idx="1051">
                   <c:v>46268</c:v>
                 </c:pt>
+                <c:pt idx="1052">
+                  <c:v>46275</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7201,7 +7207,10 @@
                   <c:v>102.66</c:v>
                 </c:pt>
                 <c:pt idx="1051">
-                  <c:v>85.6</c:v>
+                  <c:v>85.61</c:v>
+                </c:pt>
+                <c:pt idx="1052">
+                  <c:v>89.57</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10643,6 +10652,9 @@
                 </c:pt>
                 <c:pt idx="1051">
                   <c:v>46268</c:v>
+                </c:pt>
+                <c:pt idx="1052">
+                  <c:v>46275</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -22654,7 +22666,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1053"/>
+  <dimension ref="A1:L1054"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="5" bestFit="1" customWidth="1"/>
@@ -65030,7 +65042,7 @@
         <v>0.41666666666680002</v>
       </c>
       <c r="D1052" s="5" t="str">
-        <f t="shared" ref="D1052:D1053" si="42">IF(
+        <f t="shared" ref="D1052:D1054" si="42">IF(
  AND(
   B1052 &gt;= IF(
          YEAR(B1052)&gt;=2007,
@@ -65067,7 +65079,25 @@
         <v>UTC-4</v>
       </c>
       <c r="E1053" s="7">
-        <v>85.6</v>
+        <v>85.61</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1054" s="5">
+        <v>46274</v>
+      </c>
+      <c r="B1054" s="5">
+        <v>46275</v>
+      </c>
+      <c r="C1054" s="6">
+        <v>0.41666666666681201</v>
+      </c>
+      <c r="D1054" s="5" t="str">
+        <f t="shared" si="42"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E1054" s="7">
+        <v>89.57</v>
       </c>
     </row>
   </sheetData>
@@ -65079,7 +65109,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9EBD50E-72EC-42F7-90EF-D55F0BDD9D7D}">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -65143,24 +65173,8 @@
       <c r="C2" s="6">
         <v>0.41666666666674601</v>
       </c>
-      <c r="D2" s="5" t="str">
-        <f t="shared" ref="D2" si="0">IF(
- AND(
-  B2 &gt;= IF(
-         YEAR(B2)&gt;=2007,
-         DATE(YEAR(B2),3,14)-WEEKDAY(DATE(YEAR(B2),3,14),1)+1 + TIME(2,0,0),
-         DATE(YEAR(B2),4,7)-WEEKDAY(DATE(YEAR(B2),4,7),1)+1 + TIME(2,0,0)
-       ),
-  B2 &lt;  IF(
-         YEAR(B2)&gt;=2007,
-         DATE(YEAR(B2),11,7)-WEEKDAY(DATE(YEAR(B2),11,7),1)+1 + TIME(2,0,0),
-         DATE(YEAR(B2),10,31)-WEEKDAY(DATE(YEAR(B2),10,31),1) + TIME(2,0,0)
-       )
- ),
- "UTC-4",
- "UTC-5"
-)</f>
-        <v>UTC-4</v>
+      <c r="D2" s="5" t="s">
+        <v>41</v>
       </c>
       <c r="E2" s="18">
         <v>0.55600000000000005</v>
@@ -65192,51 +65206,30 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="5">
-        <f t="shared" ref="A3:B7" si="1">A2+7</f>
         <v>46205</v>
       </c>
       <c r="B3" s="5">
-        <f t="shared" si="1"/>
         <v>46209</v>
       </c>
       <c r="C3" s="6">
         <v>0.41666666666674601</v>
       </c>
-      <c r="D3" s="5" t="str">
-        <f t="shared" ref="D3:D4" si="2">IF(
- AND(
-  B3 &gt;= IF(
-         YEAR(B3)&gt;=2007,
-         DATE(YEAR(B3),3,14)-WEEKDAY(DATE(YEAR(B3),3,14),1)+1 + TIME(2,0,0),
-         DATE(YEAR(B3),4,7)-WEEKDAY(DATE(YEAR(B3),4,7),1)+1 + TIME(2,0,0)
-       ),
-  B3 &lt;  IF(
-         YEAR(B3)&gt;=2007,
-         DATE(YEAR(B3),11,7)-WEEKDAY(DATE(YEAR(B3),11,7),1)+1 + TIME(2,0,0),
-         DATE(YEAR(B3),10,31)-WEEKDAY(DATE(YEAR(B3),10,31),1) + TIME(2,0,0)
-       )
- ),
- "UTC-4",
- "UTC-5"
-)</f>
-        <v>UTC-4</v>
+      <c r="D3" s="5" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="5">
-        <f t="shared" si="1"/>
         <v>46212</v>
       </c>
       <c r="B4" s="5">
-        <f t="shared" si="1"/>
         <v>46216</v>
       </c>
       <c r="C4" s="6">
         <v>0.41666666666674601</v>
       </c>
-      <c r="D4" s="5" t="str">
-        <f t="shared" si="2"/>
-        <v>UTC-4</v>
+      <c r="D4" s="5" t="s">
+        <v>41</v>
       </c>
       <c r="E4" s="18">
         <v>0.63200000000000001</v>
@@ -65268,34 +65261,16 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="5">
-        <f t="shared" si="1"/>
         <v>46219</v>
       </c>
       <c r="B5" s="5">
-        <f t="shared" si="1"/>
         <v>46223</v>
       </c>
       <c r="C5" s="6">
         <v>0.41666666666674601</v>
       </c>
-      <c r="D5" s="5" t="str">
-        <f t="shared" ref="D5:D7" si="3">IF(
- AND(
-  B5 &gt;= IF(
-         YEAR(B5)&gt;=2007,
-         DATE(YEAR(B5),3,14)-WEEKDAY(DATE(YEAR(B5),3,14),1)+1 + TIME(2,0,0),
-         DATE(YEAR(B5),4,7)-WEEKDAY(DATE(YEAR(B5),4,7),1)+1 + TIME(2,0,0)
-       ),
-  B5 &lt;  IF(
-         YEAR(B5)&gt;=2007,
-         DATE(YEAR(B5),11,7)-WEEKDAY(DATE(YEAR(B5),11,7),1)+1 + TIME(2,0,0),
-         DATE(YEAR(B5),10,31)-WEEKDAY(DATE(YEAR(B5),10,31),1) + TIME(2,0,0)
-       )
- ),
- "UTC-4",
- "UTC-5"
-)</f>
-        <v>UTC-4</v>
+      <c r="D5" s="5" t="s">
+        <v>41</v>
       </c>
       <c r="E5" s="18">
         <v>0.40799999999999997</v>
@@ -65327,19 +65302,16 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
-        <f t="shared" ref="A6:B11" si="4">A5+7</f>
         <v>46226</v>
       </c>
       <c r="B6" s="5">
-        <f t="shared" ref="B6:B11" si="5">B5+7</f>
         <v>46230</v>
       </c>
       <c r="C6" s="6">
         <v>0.41666666666674601</v>
       </c>
-      <c r="D6" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>UTC-4</v>
+      <c r="D6" s="5" t="s">
+        <v>41</v>
       </c>
       <c r="E6" s="18">
         <v>0.55300000000000005</v>
@@ -65371,19 +65343,16 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
-        <f t="shared" si="1"/>
         <v>46233</v>
       </c>
       <c r="B7" s="5">
-        <f t="shared" si="1"/>
         <v>46237</v>
       </c>
       <c r="C7" s="6">
         <v>0.41666666666674601</v>
       </c>
-      <c r="D7" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>UTC-4</v>
+      <c r="D7" s="5" t="s">
+        <v>41</v>
       </c>
       <c r="E7" s="18">
         <v>0.60699999999999998</v>
@@ -65415,34 +65384,16 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
-        <f t="shared" si="4"/>
         <v>46240</v>
       </c>
       <c r="B8" s="5">
-        <f t="shared" si="5"/>
         <v>46244</v>
       </c>
       <c r="C8" s="6">
         <v>0.41666666666674601</v>
       </c>
-      <c r="D8" s="5" t="str">
-        <f t="shared" ref="D8:D10" si="6">IF(
- AND(
-  B8 &gt;= IF(
-         YEAR(B8)&gt;=2007,
-         DATE(YEAR(B8),3,14)-WEEKDAY(DATE(YEAR(B8),3,14),1)+1 + TIME(2,0,0),
-         DATE(YEAR(B8),4,7)-WEEKDAY(DATE(YEAR(B8),4,7),1)+1 + TIME(2,0,0)
-       ),
-  B8 &lt;  IF(
-         YEAR(B8)&gt;=2007,
-         DATE(YEAR(B8),11,7)-WEEKDAY(DATE(YEAR(B8),11,7),1)+1 + TIME(2,0,0),
-         DATE(YEAR(B8),10,31)-WEEKDAY(DATE(YEAR(B8),10,31),1) + TIME(2,0,0)
-       )
- ),
- "UTC-4",
- "UTC-5"
-)</f>
-        <v>UTC-4</v>
+      <c r="D8" s="5" t="s">
+        <v>41</v>
       </c>
       <c r="E8" s="18">
         <v>0.65300000000000002</v>
@@ -65474,19 +65425,16 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
-        <f t="shared" si="4"/>
         <v>46247</v>
       </c>
       <c r="B9" s="5">
-        <f t="shared" si="5"/>
         <v>46251</v>
       </c>
       <c r="C9" s="6">
         <v>0.41666666666674601</v>
       </c>
-      <c r="D9" s="5" t="str">
-        <f t="shared" si="6"/>
-        <v>UTC-4</v>
+      <c r="D9" s="5" t="s">
+        <v>41</v>
       </c>
       <c r="E9" s="18">
         <v>0.59099999999999997</v>
@@ -65518,19 +65466,16 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
-        <f t="shared" si="4"/>
         <v>46254</v>
       </c>
       <c r="B10" s="5">
-        <f t="shared" si="4"/>
         <v>46258</v>
       </c>
       <c r="C10" s="6">
         <v>0.41666666666674601</v>
       </c>
-      <c r="D10" s="5" t="str">
-        <f t="shared" si="6"/>
-        <v>UTC-4</v>
+      <c r="D10" s="5" t="s">
+        <v>41</v>
       </c>
       <c r="E10" s="18">
         <v>0.51800000000000002</v>
@@ -65562,34 +65507,57 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
-        <f t="shared" si="4"/>
-        <v>46261</v>
+        <v>46268</v>
       </c>
       <c r="B11" s="5">
-        <f t="shared" si="5"/>
-        <v>46265</v>
+        <v>46273</v>
       </c>
       <c r="C11" s="6">
         <v>0.41666666666674601</v>
       </c>
-      <c r="D11" s="5" t="str">
-        <f t="shared" ref="D11" si="7">IF(
- AND(
-  B11 &gt;= IF(
-         YEAR(B11)&gt;=2007,
-         DATE(YEAR(B11),3,14)-WEEKDAY(DATE(YEAR(B11),3,14),1)+1 + TIME(2,0,0),
-         DATE(YEAR(B11),4,7)-WEEKDAY(DATE(YEAR(B11),4,7),1)+1 + TIME(2,0,0)
-       ),
-  B11 &lt;  IF(
-         YEAR(B11)&gt;=2007,
-         DATE(YEAR(B11),11,7)-WEEKDAY(DATE(YEAR(B11),11,7),1)+1 + TIME(2,0,0),
-         DATE(YEAR(B11),10,31)-WEEKDAY(DATE(YEAR(B11),10,31),1) + TIME(2,0,0)
-       )
- ),
- "UTC-4",
- "UTC-5"
-)</f>
-        <v>UTC-4</v>
+      <c r="D11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" s="18">
+        <v>0.56599999999999995</v>
+      </c>
+      <c r="F11" s="18">
+        <v>0.433</v>
+      </c>
+      <c r="G11" s="18">
+        <v>0.19639999999999999</v>
+      </c>
+      <c r="H11" s="18">
+        <v>0.1429</v>
+      </c>
+      <c r="I11" s="18">
+        <v>0.03</v>
+      </c>
+      <c r="J11" s="18">
+        <v>1.67E-2</v>
+      </c>
+      <c r="K11" s="18">
+        <v>0.18</v>
+      </c>
+      <c r="L11" s="18">
+        <v>-5.67E-2</v>
+      </c>
+      <c r="M11" s="18">
+        <v>8.5099999999999995E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A12" s="5">
+        <v>46275</v>
+      </c>
+      <c r="B12" s="5">
+        <v>46279</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0.41666666666674601</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/behavior/NAAIM Exposure Index.xlsx
+++ b/data_lake/behavior/NAAIM Exposure Index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/behavior/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2415F98-7765-F74B-B77A-5ED244BC991D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C4CE3DA-DF27-A048-A1DD-72519085DACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15020" yWindow="780" windowWidth="20980" windowHeight="20700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4044,6 +4044,9 @@
                 <c:pt idx="1052">
                   <c:v>46275</c:v>
                 </c:pt>
+                <c:pt idx="1053">
+                  <c:v>46282</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10655,6 +10658,9 @@
                 </c:pt>
                 <c:pt idx="1052">
                   <c:v>46275</c:v>
+                </c:pt>
+                <c:pt idx="1053">
+                  <c:v>46282</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -22666,7 +22672,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1054"/>
+  <dimension ref="A1:L1055"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="5" bestFit="1" customWidth="1"/>
@@ -65098,6 +65104,36 @@
       </c>
       <c r="E1054" s="7">
         <v>89.57</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1055" s="5">
+        <v>46281</v>
+      </c>
+      <c r="B1055" s="5">
+        <v>46282</v>
+      </c>
+      <c r="C1055" s="6">
+        <v>0.41666666666681801</v>
+      </c>
+      <c r="D1055" s="5" t="str">
+        <f t="shared" ref="D1055" si="43">IF(
+ AND(
+  B1055 &gt;= IF(
+         YEAR(B1055)&gt;=2007,
+         DATE(YEAR(B1055),3,14)-WEEKDAY(DATE(YEAR(B1055),3,14),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B1055),4,7)-WEEKDAY(DATE(YEAR(B1055),4,7),1)+1 + TIME(2,0,0)
+       ),
+  B1055 &lt;  IF(
+         YEAR(B1055)&gt;=2007,
+         DATE(YEAR(B1055),11,7)-WEEKDAY(DATE(YEAR(B1055),11,7),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B1055),10,31)-WEEKDAY(DATE(YEAR(B1055),10,31),1) + TIME(2,0,0)
+       )
+ ),
+ "UTC-4",
+ "UTC-5"
+)</f>
+        <v>UTC-4</v>
       </c>
     </row>
   </sheetData>
@@ -65558,6 +65594,33 @@
       </c>
       <c r="D12" s="5" t="s">
         <v>41</v>
+      </c>
+      <c r="E12" s="18">
+        <v>0.56799999999999995</v>
+      </c>
+      <c r="F12" s="18">
+        <v>0.432</v>
+      </c>
+      <c r="G12" s="18">
+        <v>0.16070000000000001</v>
+      </c>
+      <c r="H12" s="18">
+        <v>0.1071</v>
+      </c>
+      <c r="I12" s="18">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="J12" s="18">
+        <v>0.05</v>
+      </c>
+      <c r="K12" s="18">
+        <v>0.18</v>
+      </c>
+      <c r="L12" s="18">
+        <v>-5.3600000000000002E-2</v>
+      </c>
+      <c r="M12" s="18">
+        <v>8.0399999999999999E-2</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/behavior/NAAIM Exposure Index.xlsx
+++ b/data_lake/behavior/NAAIM Exposure Index.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/behavior/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C4CE3DA-DF27-A048-A1DD-72519085DACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6A069E-1B22-DB45-8EE5-32B309C6D182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15020" yWindow="780" windowWidth="20980" windowHeight="20700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15020" yWindow="780" windowWidth="20980" windowHeight="20680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NAAIM" sheetId="1" r:id="rId1"/>
@@ -7213,7 +7213,10 @@
                   <c:v>85.61</c:v>
                 </c:pt>
                 <c:pt idx="1052">
-                  <c:v>89.57</c:v>
+                  <c:v>87.19</c:v>
+                </c:pt>
+                <c:pt idx="1053">
+                  <c:v>71.92</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -65103,7 +65106,7 @@
         <v>UTC-4</v>
       </c>
       <c r="E1054" s="7">
-        <v>89.57</v>
+        <v>87.19</v>
       </c>
     </row>
     <row r="1055" spans="1:12" x14ac:dyDescent="0.2">
@@ -65134,6 +65137,9 @@
  "UTC-5"
 )</f>
         <v>UTC-4</v>
+      </c>
+      <c r="E1055" s="7">
+        <v>71.92</v>
       </c>
     </row>
   </sheetData>
